--- a/relatorios/controle_patrimonial.xlsx
+++ b/relatorios/controle_patrimonial.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\controle_estoque_db\relatorios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8960B2E5-A43C-4BCE-BCA3-5D601E2FEB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="25650" windowHeight="10740"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="25650" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Estoque" sheetId="1" r:id="rId1"/>
@@ -17,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="55">
   <si>
     <t>SITUAÇÃO</t>
   </si>
@@ -181,40 +187,13 @@
     <t>ADM01</t>
   </si>
   <si>
-    <t>ADM02</t>
-  </si>
-  <si>
-    <t>ADM03</t>
-  </si>
-  <si>
-    <t>ADM04</t>
-  </si>
-  <si>
-    <t>ADM05</t>
-  </si>
-  <si>
-    <t>ADM06</t>
-  </si>
-  <si>
-    <t>ADM07</t>
-  </si>
-  <si>
-    <t>ADM08</t>
-  </si>
-  <si>
-    <t>ADM09</t>
-  </si>
-  <si>
-    <t>ADM10</t>
-  </si>
-  <si>
     <t>CEAD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -850,14 +829,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -947,7 +926,7 @@
         <v>45927</v>
       </c>
       <c r="H3" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -971,7 +950,7 @@
         <v>45927</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -995,7 +974,7 @@
         <v>45927</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1019,7 +998,7 @@
         <v>45927</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1034,7 +1013,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F7" s="48">
         <v>44693</v>
@@ -1043,7 +1022,7 @@
         <v>45927</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1058,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F8" s="48">
         <v>44693</v>
@@ -1067,7 +1046,7 @@
         <v>45927</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1082,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F9" s="48">
         <v>44693</v>
@@ -1091,7 +1070,7 @@
         <v>45927</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1106,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F10" s="48">
         <v>44693</v>
@@ -1115,7 +1094,7 @@
         <v>45927</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1130,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F11" s="48">
         <v>44693</v>
@@ -1139,7 +1118,7 @@
         <v>45927</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1154,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F12" s="48">
         <v>44693</v>
@@ -1162,7 +1141,9 @@
       <c r="G12" s="48">
         <v>45927</v>
       </c>
-      <c r="H12" s="46"/>
+      <c r="H12" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
@@ -1176,7 +1157,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F13" s="48">
         <v>44693</v>
@@ -1184,7 +1165,9 @@
       <c r="G13" s="48">
         <v>45927</v>
       </c>
-      <c r="H13" s="46"/>
+      <c r="H13" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -1198,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F14" s="48">
         <v>44693</v>
@@ -1206,7 +1189,9 @@
       <c r="G14" s="48">
         <v>45927</v>
       </c>
-      <c r="H14" s="46"/>
+      <c r="H14" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
@@ -1220,7 +1205,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F15" s="48">
         <v>44693</v>
@@ -1228,7 +1213,9 @@
       <c r="G15" s="48">
         <v>45927</v>
       </c>
-      <c r="H15" s="46"/>
+      <c r="H15" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
@@ -1242,7 +1229,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F16" s="48">
         <v>44693</v>
@@ -1250,7 +1237,9 @@
       <c r="G16" s="48">
         <v>45927</v>
       </c>
-      <c r="H16" s="46"/>
+      <c r="H16" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
@@ -1264,7 +1253,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F17" s="48">
         <v>44693</v>
@@ -1272,7 +1261,9 @@
       <c r="G17" s="48">
         <v>45927</v>
       </c>
-      <c r="H17" s="46"/>
+      <c r="H17" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
@@ -1286,7 +1277,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F18" s="48">
         <v>44693</v>
@@ -1294,7 +1285,9 @@
       <c r="G18" s="48">
         <v>45927</v>
       </c>
-      <c r="H18" s="46"/>
+      <c r="H18" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
@@ -1308,7 +1301,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F19" s="48">
         <v>44693</v>
@@ -1316,7 +1309,9 @@
       <c r="G19" s="48">
         <v>45927</v>
       </c>
-      <c r="H19" s="46"/>
+      <c r="H19" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
@@ -1330,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F20" s="48">
         <v>44693</v>
@@ -1338,7 +1333,9 @@
       <c r="G20" s="48">
         <v>45927</v>
       </c>
-      <c r="H20" s="46"/>
+      <c r="H20" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
@@ -1352,7 +1349,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F21" s="48">
         <v>44693</v>
@@ -1360,7 +1357,9 @@
       <c r="G21" s="48">
         <v>45927</v>
       </c>
-      <c r="H21" s="46"/>
+      <c r="H21" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
@@ -1374,7 +1373,7 @@
         <v>17</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F22" s="48">
         <v>44693</v>
@@ -1382,7 +1381,9 @@
       <c r="G22" s="48">
         <v>45927</v>
       </c>
-      <c r="H22" s="46"/>
+      <c r="H22" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
@@ -1396,7 +1397,7 @@
         <v>17</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F23" s="48">
         <v>44693</v>
@@ -1404,7 +1405,9 @@
       <c r="G23" s="48">
         <v>45927</v>
       </c>
-      <c r="H23" s="46"/>
+      <c r="H23" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -1418,7 +1421,7 @@
         <v>17</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F24" s="48">
         <v>44693</v>
@@ -1426,7 +1429,9 @@
       <c r="G24" s="48">
         <v>45927</v>
       </c>
-      <c r="H24" s="46"/>
+      <c r="H24" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
@@ -1440,7 +1445,7 @@
         <v>17</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F25" s="48">
         <v>44693</v>
@@ -1448,7 +1453,9 @@
       <c r="G25" s="48">
         <v>45927</v>
       </c>
-      <c r="H25" s="46"/>
+      <c r="H25" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
@@ -1462,7 +1469,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F26" s="48">
         <v>44693</v>
@@ -1470,7 +1477,9 @@
       <c r="G26" s="48">
         <v>45927</v>
       </c>
-      <c r="H26" s="46"/>
+      <c r="H26" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
@@ -1484,7 +1493,7 @@
         <v>17</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F27" s="48">
         <v>44693</v>
@@ -1492,7 +1501,9 @@
       <c r="G27" s="48">
         <v>45927</v>
       </c>
-      <c r="H27" s="46"/>
+      <c r="H27" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
@@ -1506,7 +1517,7 @@
         <v>17</v>
       </c>
       <c r="E28" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F28" s="48">
         <v>44693</v>
@@ -1514,7 +1525,9 @@
       <c r="G28" s="48">
         <v>45927</v>
       </c>
-      <c r="H28" s="46"/>
+      <c r="H28" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
@@ -1528,7 +1541,7 @@
         <v>17</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F29" s="48">
         <v>44693</v>
@@ -1536,7 +1549,9 @@
       <c r="G29" s="48">
         <v>45927</v>
       </c>
-      <c r="H29" s="46"/>
+      <c r="H29" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
@@ -1550,7 +1565,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F30" s="48">
         <v>44693</v>
@@ -1558,7 +1573,9 @@
       <c r="G30" s="48">
         <v>45927</v>
       </c>
-      <c r="H30" s="46"/>
+      <c r="H30" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
@@ -1572,7 +1589,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F31" s="48">
         <v>44693</v>
@@ -1580,7 +1597,9 @@
       <c r="G31" s="48">
         <v>45927</v>
       </c>
-      <c r="H31" s="46"/>
+      <c r="H31" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
@@ -1594,7 +1613,7 @@
         <v>17</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F32" s="48">
         <v>44693</v>
@@ -1602,7 +1621,9 @@
       <c r="G32" s="48">
         <v>45927</v>
       </c>
-      <c r="H32" s="46"/>
+      <c r="H32" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
@@ -1616,7 +1637,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F33" s="48">
         <v>44693</v>
@@ -1624,7 +1645,9 @@
       <c r="G33" s="48">
         <v>45927</v>
       </c>
-      <c r="H33" s="46"/>
+      <c r="H33" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
@@ -1638,7 +1661,7 @@
         <v>17</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F34" s="48">
         <v>44693</v>
@@ -1646,7 +1669,9 @@
       <c r="G34" s="48">
         <v>45927</v>
       </c>
-      <c r="H34" s="46"/>
+      <c r="H34" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
@@ -1660,7 +1685,7 @@
         <v>17</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F35" s="48">
         <v>44693</v>
@@ -1668,7 +1693,9 @@
       <c r="G35" s="48">
         <v>45927</v>
       </c>
-      <c r="H35" s="46"/>
+      <c r="H35" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
@@ -1682,7 +1709,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F36" s="48">
         <v>44693</v>
@@ -1690,7 +1717,9 @@
       <c r="G36" s="48">
         <v>45927</v>
       </c>
-      <c r="H36" s="46"/>
+      <c r="H36" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
@@ -1704,7 +1733,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F37" s="48">
         <v>44693</v>
@@ -1712,7 +1741,9 @@
       <c r="G37" s="48">
         <v>45927</v>
       </c>
-      <c r="H37" s="46"/>
+      <c r="H37" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
@@ -1726,7 +1757,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F38" s="48">
         <v>44693</v>
@@ -1734,7 +1765,9 @@
       <c r="G38" s="48">
         <v>45927</v>
       </c>
-      <c r="H38" s="46"/>
+      <c r="H38" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
@@ -1748,7 +1781,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F39" s="48">
         <v>44693</v>
@@ -1756,7 +1789,9 @@
       <c r="G39" s="48">
         <v>45927</v>
       </c>
-      <c r="H39" s="46"/>
+      <c r="H39" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
@@ -1770,7 +1805,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F40" s="48">
         <v>44693</v>
@@ -1778,7 +1813,9 @@
       <c r="G40" s="48">
         <v>45927</v>
       </c>
-      <c r="H40" s="46"/>
+      <c r="H40" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="41" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
@@ -1792,7 +1829,7 @@
         <v>25</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F41" s="48">
         <v>44693</v>
@@ -1800,7 +1837,9 @@
       <c r="G41" s="48">
         <v>45927</v>
       </c>
-      <c r="H41" s="46"/>
+      <c r="H41" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="42" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
@@ -1814,7 +1853,7 @@
         <v>25</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F42" s="48">
         <v>44693</v>
@@ -1822,7 +1861,9 @@
       <c r="G42" s="48">
         <v>45927</v>
       </c>
-      <c r="H42" s="46"/>
+      <c r="H42" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
@@ -1836,7 +1877,7 @@
         <v>25</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F43" s="48">
         <v>44693</v>
@@ -1844,7 +1885,9 @@
       <c r="G43" s="48">
         <v>45927</v>
       </c>
-      <c r="H43" s="46"/>
+      <c r="H43" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="44" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
@@ -1858,7 +1901,7 @@
         <v>25</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F44" s="48">
         <v>44693</v>
@@ -1866,7 +1909,9 @@
       <c r="G44" s="48">
         <v>45927</v>
       </c>
-      <c r="H44" s="46"/>
+      <c r="H44" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="45" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
@@ -1880,7 +1925,7 @@
         <v>25</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F45" s="48">
         <v>44693</v>
@@ -1888,7 +1933,9 @@
       <c r="G45" s="48">
         <v>45927</v>
       </c>
-      <c r="H45" s="46"/>
+      <c r="H45" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="46" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
@@ -1902,7 +1949,7 @@
         <v>25</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F46" s="48">
         <v>44693</v>
@@ -1910,7 +1957,9 @@
       <c r="G46" s="48">
         <v>45927</v>
       </c>
-      <c r="H46" s="46"/>
+      <c r="H46" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
@@ -1924,7 +1973,7 @@
         <v>25</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F47" s="48">
         <v>44693</v>
@@ -1932,7 +1981,9 @@
       <c r="G47" s="48">
         <v>45927</v>
       </c>
-      <c r="H47" s="46"/>
+      <c r="H47" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="48" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
@@ -1946,7 +1997,7 @@
         <v>25</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F48" s="48">
         <v>44693</v>
@@ -1954,7 +2005,9 @@
       <c r="G48" s="48">
         <v>45927</v>
       </c>
-      <c r="H48" s="46"/>
+      <c r="H48" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="49" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
@@ -1968,7 +2021,7 @@
         <v>25</v>
       </c>
       <c r="E49" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F49" s="48">
         <v>44693</v>
@@ -1976,7 +2029,9 @@
       <c r="G49" s="48">
         <v>45927</v>
       </c>
-      <c r="H49" s="46"/>
+      <c r="H49" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="50" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
@@ -1990,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F50" s="48">
         <v>44693</v>
@@ -1998,7 +2053,9 @@
       <c r="G50" s="48">
         <v>45927</v>
       </c>
-      <c r="H50" s="46"/>
+      <c r="H50" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="51" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
@@ -2012,7 +2069,7 @@
         <v>25</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F51" s="48">
         <v>44693</v>
@@ -2020,7 +2077,9 @@
       <c r="G51" s="48">
         <v>45927</v>
       </c>
-      <c r="H51" s="46"/>
+      <c r="H51" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="52" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
@@ -2034,7 +2093,7 @@
         <v>25</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F52" s="48">
         <v>44693</v>
@@ -2042,7 +2101,9 @@
       <c r="G52" s="48">
         <v>45927</v>
       </c>
-      <c r="H52" s="46"/>
+      <c r="H52" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="53" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
@@ -2056,7 +2117,7 @@
         <v>25</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F53" s="48">
         <v>44693</v>
@@ -2064,7 +2125,9 @@
       <c r="G53" s="48">
         <v>45927</v>
       </c>
-      <c r="H53" s="46"/>
+      <c r="H53" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
@@ -2078,7 +2141,7 @@
         <v>25</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F54" s="48">
         <v>44693</v>
@@ -2086,7 +2149,9 @@
       <c r="G54" s="48">
         <v>45927</v>
       </c>
-      <c r="H54" s="46"/>
+      <c r="H54" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="55" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
@@ -2100,7 +2165,7 @@
         <v>25</v>
       </c>
       <c r="E55" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F55" s="48">
         <v>44693</v>
@@ -2108,7 +2173,9 @@
       <c r="G55" s="48">
         <v>45927</v>
       </c>
-      <c r="H55" s="46"/>
+      <c r="H55" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="56" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
@@ -2122,7 +2189,7 @@
         <v>25</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F56" s="48">
         <v>44693</v>
@@ -2130,7 +2197,9 @@
       <c r="G56" s="48">
         <v>45927</v>
       </c>
-      <c r="H56" s="46"/>
+      <c r="H56" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="57" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
@@ -2144,7 +2213,7 @@
         <v>25</v>
       </c>
       <c r="E57" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F57" s="48">
         <v>44693</v>
@@ -2152,7 +2221,9 @@
       <c r="G57" s="48">
         <v>45927</v>
       </c>
-      <c r="H57" s="46"/>
+      <c r="H57" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="58" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
@@ -2166,7 +2237,7 @@
         <v>25</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F58" s="48">
         <v>44693</v>
@@ -2174,7 +2245,9 @@
       <c r="G58" s="48">
         <v>45927</v>
       </c>
-      <c r="H58" s="46"/>
+      <c r="H58" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="59" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
@@ -2188,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="E59" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F59" s="48">
         <v>44693</v>
@@ -2196,7 +2269,9 @@
       <c r="G59" s="48">
         <v>45927</v>
       </c>
-      <c r="H59" s="46"/>
+      <c r="H59" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="60" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
@@ -2210,7 +2285,7 @@
         <v>25</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F60" s="48">
         <v>44693</v>
@@ -2218,7 +2293,9 @@
       <c r="G60" s="48">
         <v>45927</v>
       </c>
-      <c r="H60" s="46"/>
+      <c r="H60" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="61" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
@@ -2232,7 +2309,7 @@
         <v>25</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F61" s="48">
         <v>44693</v>
@@ -2240,7 +2317,9 @@
       <c r="G61" s="48">
         <v>45927</v>
       </c>
-      <c r="H61" s="46"/>
+      <c r="H61" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="62" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
@@ -2254,7 +2333,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F62" s="48">
         <v>44693</v>
@@ -2262,7 +2341,9 @@
       <c r="G62" s="48">
         <v>45927</v>
       </c>
-      <c r="H62" s="46"/>
+      <c r="H62" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="63" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
@@ -2276,7 +2357,7 @@
         <v>25</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F63" s="48">
         <v>44693</v>
@@ -2284,7 +2365,9 @@
       <c r="G63" s="48">
         <v>45927</v>
       </c>
-      <c r="H63" s="46"/>
+      <c r="H63" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="64" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
@@ -2298,7 +2381,7 @@
         <v>25</v>
       </c>
       <c r="E64" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F64" s="48">
         <v>44693</v>
@@ -2306,7 +2389,9 @@
       <c r="G64" s="48">
         <v>45927</v>
       </c>
-      <c r="H64" s="46"/>
+      <c r="H64" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="65" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
@@ -2320,7 +2405,7 @@
         <v>25</v>
       </c>
       <c r="E65" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F65" s="48">
         <v>44693</v>
@@ -2328,7 +2413,9 @@
       <c r="G65" s="48">
         <v>45927</v>
       </c>
-      <c r="H65" s="46"/>
+      <c r="H65" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="66" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
@@ -2342,7 +2429,7 @@
         <v>25</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F66" s="48">
         <v>44693</v>
@@ -2350,7 +2437,9 @@
       <c r="G66" s="48">
         <v>45927</v>
       </c>
-      <c r="H66" s="46"/>
+      <c r="H66" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="67" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
@@ -2364,7 +2453,7 @@
         <v>25</v>
       </c>
       <c r="E67" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F67" s="48">
         <v>44693</v>
@@ -2372,7 +2461,9 @@
       <c r="G67" s="48">
         <v>45927</v>
       </c>
-      <c r="H67" s="46"/>
+      <c r="H67" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="68" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
@@ -2386,7 +2477,7 @@
         <v>25</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F68" s="48">
         <v>44693</v>
@@ -2394,7 +2485,9 @@
       <c r="G68" s="48">
         <v>45927</v>
       </c>
-      <c r="H68" s="46"/>
+      <c r="H68" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="69" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
@@ -2408,7 +2501,7 @@
         <v>25</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F69" s="48">
         <v>44693</v>
@@ -2416,7 +2509,9 @@
       <c r="G69" s="48">
         <v>45927</v>
       </c>
-      <c r="H69" s="46"/>
+      <c r="H69" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="70" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
@@ -2430,7 +2525,7 @@
         <v>25</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F70" s="48">
         <v>44693</v>
@@ -2438,7 +2533,9 @@
       <c r="G70" s="48">
         <v>45927</v>
       </c>
-      <c r="H70" s="46"/>
+      <c r="H70" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="71" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
@@ -2452,7 +2549,7 @@
         <v>25</v>
       </c>
       <c r="E71" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F71" s="48">
         <v>44693</v>
@@ -2460,7 +2557,9 @@
       <c r="G71" s="48">
         <v>45927</v>
       </c>
-      <c r="H71" s="46"/>
+      <c r="H71" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="72" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
@@ -2474,7 +2573,7 @@
         <v>25</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F72" s="48">
         <v>44693</v>
@@ -2482,7 +2581,9 @@
       <c r="G72" s="48">
         <v>45927</v>
       </c>
-      <c r="H72" s="46"/>
+      <c r="H72" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="73" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
@@ -2496,7 +2597,7 @@
         <v>25</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F73" s="48">
         <v>44693</v>
@@ -2504,7 +2605,9 @@
       <c r="G73" s="48">
         <v>45927</v>
       </c>
-      <c r="H73" s="46"/>
+      <c r="H73" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="74" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
@@ -2518,7 +2621,7 @@
         <v>25</v>
       </c>
       <c r="E74" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F74" s="48">
         <v>44693</v>
@@ -2526,7 +2629,9 @@
       <c r="G74" s="48">
         <v>45927</v>
       </c>
-      <c r="H74" s="46"/>
+      <c r="H74" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="75" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
@@ -2540,7 +2645,7 @@
         <v>25</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F75" s="48">
         <v>44693</v>
@@ -2548,7 +2653,9 @@
       <c r="G75" s="48">
         <v>45927</v>
       </c>
-      <c r="H75" s="46"/>
+      <c r="H75" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="76" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
@@ -2562,7 +2669,7 @@
         <v>25</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F76" s="48">
         <v>44693</v>
@@ -2570,7 +2677,9 @@
       <c r="G76" s="48">
         <v>45927</v>
       </c>
-      <c r="H76" s="46"/>
+      <c r="H76" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="77" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
@@ -2584,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="E77" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F77" s="48">
         <v>44693</v>
@@ -2592,7 +2701,9 @@
       <c r="G77" s="48">
         <v>45927</v>
       </c>
-      <c r="H77" s="46"/>
+      <c r="H77" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="78" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
@@ -2606,7 +2717,7 @@
         <v>25</v>
       </c>
       <c r="E78" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F78" s="48">
         <v>44693</v>
@@ -2614,7 +2725,9 @@
       <c r="G78" s="48">
         <v>45927</v>
       </c>
-      <c r="H78" s="46"/>
+      <c r="H78" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="79" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
@@ -2628,7 +2741,7 @@
         <v>25</v>
       </c>
       <c r="E79" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F79" s="48">
         <v>44693</v>
@@ -2636,7 +2749,9 @@
       <c r="G79" s="48">
         <v>45927</v>
       </c>
-      <c r="H79" s="46"/>
+      <c r="H79" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="80" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
@@ -2650,7 +2765,7 @@
         <v>25</v>
       </c>
       <c r="E80" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F80" s="48">
         <v>44693</v>
@@ -2658,7 +2773,9 @@
       <c r="G80" s="48">
         <v>45927</v>
       </c>
-      <c r="H80" s="46"/>
+      <c r="H80" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="81" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
@@ -2672,7 +2789,7 @@
         <v>25</v>
       </c>
       <c r="E81" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F81" s="48">
         <v>44693</v>
@@ -2680,7 +2797,9 @@
       <c r="G81" s="48">
         <v>45927</v>
       </c>
-      <c r="H81" s="46"/>
+      <c r="H81" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="82" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
@@ -2694,7 +2813,7 @@
         <v>25</v>
       </c>
       <c r="E82" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F82" s="48">
         <v>44693</v>
@@ -2702,7 +2821,9 @@
       <c r="G82" s="48">
         <v>45927</v>
       </c>
-      <c r="H82" s="46"/>
+      <c r="H82" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
@@ -2716,7 +2837,7 @@
         <v>25</v>
       </c>
       <c r="E83" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F83" s="48">
         <v>44693</v>
@@ -2724,7 +2845,9 @@
       <c r="G83" s="48">
         <v>45927</v>
       </c>
-      <c r="H83" s="46"/>
+      <c r="H83" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
@@ -2738,7 +2861,7 @@
         <v>25</v>
       </c>
       <c r="E84" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F84" s="48">
         <v>44693</v>
@@ -2746,7 +2869,9 @@
       <c r="G84" s="48">
         <v>45927</v>
       </c>
-      <c r="H84" s="46"/>
+      <c r="H84" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="85" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
@@ -2760,7 +2885,7 @@
         <v>25</v>
       </c>
       <c r="E85" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F85" s="48">
         <v>44693</v>
@@ -2768,7 +2893,9 @@
       <c r="G85" s="48">
         <v>45927</v>
       </c>
-      <c r="H85" s="46"/>
+      <c r="H85" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="86" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
@@ -2782,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="E86" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F86" s="48">
         <v>44693</v>
@@ -2790,7 +2917,9 @@
       <c r="G86" s="48">
         <v>45927</v>
       </c>
-      <c r="H86" s="46"/>
+      <c r="H86" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="87" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
@@ -2804,7 +2933,7 @@
         <v>25</v>
       </c>
       <c r="E87" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F87" s="48">
         <v>44693</v>
@@ -2812,7 +2941,9 @@
       <c r="G87" s="48">
         <v>45927</v>
       </c>
-      <c r="H87" s="46"/>
+      <c r="H87" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="88" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
@@ -2826,7 +2957,7 @@
         <v>25</v>
       </c>
       <c r="E88" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F88" s="48">
         <v>44693</v>
@@ -2834,7 +2965,9 @@
       <c r="G88" s="48">
         <v>45927</v>
       </c>
-      <c r="H88" s="46"/>
+      <c r="H88" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="89" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
@@ -2848,7 +2981,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F89" s="48">
         <v>44693</v>
@@ -2856,7 +2989,9 @@
       <c r="G89" s="48">
         <v>45927</v>
       </c>
-      <c r="H89" s="46"/>
+      <c r="H89" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="90" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
@@ -2870,7 +3005,7 @@
         <v>25</v>
       </c>
       <c r="E90" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F90" s="48">
         <v>44693</v>
@@ -2878,7 +3013,9 @@
       <c r="G90" s="48">
         <v>45927</v>
       </c>
-      <c r="H90" s="46"/>
+      <c r="H90" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="91" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
@@ -2892,7 +3029,7 @@
         <v>37</v>
       </c>
       <c r="E91" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F91" s="48">
         <v>44693</v>
@@ -2900,7 +3037,9 @@
       <c r="G91" s="48">
         <v>45927</v>
       </c>
-      <c r="H91" s="46"/>
+      <c r="H91" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="92" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
@@ -2914,7 +3053,7 @@
         <v>37</v>
       </c>
       <c r="E92" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F92" s="48">
         <v>44693</v>
@@ -2922,7 +3061,9 @@
       <c r="G92" s="48">
         <v>45927</v>
       </c>
-      <c r="H92" s="46"/>
+      <c r="H92" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="93" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
@@ -2936,7 +3077,7 @@
         <v>37</v>
       </c>
       <c r="E93" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F93" s="48">
         <v>44693</v>
@@ -2944,7 +3085,9 @@
       <c r="G93" s="48">
         <v>45927</v>
       </c>
-      <c r="H93" s="46"/>
+      <c r="H93" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="94" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
@@ -2958,7 +3101,7 @@
         <v>37</v>
       </c>
       <c r="E94" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F94" s="48">
         <v>44693</v>
@@ -2966,7 +3109,9 @@
       <c r="G94" s="48">
         <v>45927</v>
       </c>
-      <c r="H94" s="46"/>
+      <c r="H94" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="95" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
@@ -2980,7 +3125,7 @@
         <v>37</v>
       </c>
       <c r="E95" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F95" s="48">
         <v>44693</v>
@@ -2988,7 +3133,9 @@
       <c r="G95" s="48">
         <v>45927</v>
       </c>
-      <c r="H95" s="46"/>
+      <c r="H95" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="96" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
@@ -3002,7 +3149,7 @@
         <v>37</v>
       </c>
       <c r="E96" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F96" s="48">
         <v>44693</v>
@@ -3010,7 +3157,9 @@
       <c r="G96" s="48">
         <v>45927</v>
       </c>
-      <c r="H96" s="46"/>
+      <c r="H96" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="97" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
@@ -3024,7 +3173,7 @@
         <v>37</v>
       </c>
       <c r="E97" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F97" s="48">
         <v>44693</v>
@@ -3032,7 +3181,9 @@
       <c r="G97" s="48">
         <v>45927</v>
       </c>
-      <c r="H97" s="46"/>
+      <c r="H97" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="98" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
@@ -3046,7 +3197,7 @@
         <v>37</v>
       </c>
       <c r="E98" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F98" s="48">
         <v>44693</v>
@@ -3054,7 +3205,9 @@
       <c r="G98" s="48">
         <v>45927</v>
       </c>
-      <c r="H98" s="46"/>
+      <c r="H98" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="99" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
@@ -3068,7 +3221,7 @@
         <v>37</v>
       </c>
       <c r="E99" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F99" s="48">
         <v>44693</v>
@@ -3076,7 +3229,9 @@
       <c r="G99" s="48">
         <v>45927</v>
       </c>
-      <c r="H99" s="46"/>
+      <c r="H99" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="100" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
@@ -3090,7 +3245,7 @@
         <v>37</v>
       </c>
       <c r="E100" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F100" s="48">
         <v>44693</v>
@@ -3098,7 +3253,9 @@
       <c r="G100" s="48">
         <v>45927</v>
       </c>
-      <c r="H100" s="46"/>
+      <c r="H100" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="101" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
@@ -3112,7 +3269,7 @@
         <v>37</v>
       </c>
       <c r="E101" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F101" s="48">
         <v>44693</v>
@@ -3120,7 +3277,9 @@
       <c r="G101" s="48">
         <v>45927</v>
       </c>
-      <c r="H101" s="46"/>
+      <c r="H101" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="102" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
@@ -3134,7 +3293,7 @@
         <v>37</v>
       </c>
       <c r="E102" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F102" s="48">
         <v>44693</v>
@@ -3142,7 +3301,9 @@
       <c r="G102" s="48">
         <v>45927</v>
       </c>
-      <c r="H102" s="46"/>
+      <c r="H102" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="103" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
@@ -3156,7 +3317,7 @@
         <v>37</v>
       </c>
       <c r="E103" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F103" s="48">
         <v>44693</v>
@@ -3164,7 +3325,9 @@
       <c r="G103" s="48">
         <v>45927</v>
       </c>
-      <c r="H103" s="46"/>
+      <c r="H103" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="104" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
@@ -3178,7 +3341,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F104" s="48">
         <v>44693</v>
@@ -3186,7 +3349,9 @@
       <c r="G104" s="48">
         <v>45927</v>
       </c>
-      <c r="H104" s="46"/>
+      <c r="H104" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="105" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
@@ -3200,7 +3365,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F105" s="48">
         <v>44693</v>
@@ -3208,7 +3373,9 @@
       <c r="G105" s="48">
         <v>45927</v>
       </c>
-      <c r="H105" s="46"/>
+      <c r="H105" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="106" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
@@ -3222,7 +3389,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F106" s="48">
         <v>44693</v>
@@ -3230,7 +3397,9 @@
       <c r="G106" s="48">
         <v>45927</v>
       </c>
-      <c r="H106" s="46"/>
+      <c r="H106" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="107" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="20" t="s">
@@ -3244,7 +3413,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F107" s="48">
         <v>44693</v>
@@ -3252,7 +3421,9 @@
       <c r="G107" s="48">
         <v>45927</v>
       </c>
-      <c r="H107" s="46"/>
+      <c r="H107" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="108" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
@@ -3266,7 +3437,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F108" s="48">
         <v>44693</v>
@@ -3274,7 +3445,9 @@
       <c r="G108" s="48">
         <v>45927</v>
       </c>
-      <c r="H108" s="46"/>
+      <c r="H108" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="109" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
@@ -3288,7 +3461,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F109" s="48">
         <v>44693</v>
@@ -3296,7 +3469,9 @@
       <c r="G109" s="48">
         <v>45927</v>
       </c>
-      <c r="H109" s="46"/>
+      <c r="H109" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="110" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
@@ -3310,7 +3485,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F110" s="48">
         <v>44693</v>
@@ -3318,7 +3493,9 @@
       <c r="G110" s="48">
         <v>45927</v>
       </c>
-      <c r="H110" s="46"/>
+      <c r="H110" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="111" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20" t="s">
@@ -3332,7 +3509,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F111" s="48">
         <v>44693</v>
@@ -3340,7 +3517,9 @@
       <c r="G111" s="48">
         <v>45927</v>
       </c>
-      <c r="H111" s="46"/>
+      <c r="H111" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="112" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
@@ -3354,7 +3533,7 @@
         <v>37</v>
       </c>
       <c r="E112" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F112" s="48">
         <v>44693</v>
@@ -3362,7 +3541,9 @@
       <c r="G112" s="48">
         <v>45927</v>
       </c>
-      <c r="H112" s="46"/>
+      <c r="H112" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="113" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
@@ -3376,7 +3557,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F113" s="48">
         <v>44693</v>
@@ -3384,7 +3565,9 @@
       <c r="G113" s="48">
         <v>45927</v>
       </c>
-      <c r="H113" s="46"/>
+      <c r="H113" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="114" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
@@ -3398,7 +3581,7 @@
         <v>37</v>
       </c>
       <c r="E114" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F114" s="48">
         <v>44693</v>
@@ -3406,7 +3589,9 @@
       <c r="G114" s="48">
         <v>45927</v>
       </c>
-      <c r="H114" s="46"/>
+      <c r="H114" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="115" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
@@ -3420,7 +3605,7 @@
         <v>37</v>
       </c>
       <c r="E115" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F115" s="48">
         <v>44693</v>
@@ -3428,7 +3613,9 @@
       <c r="G115" s="48">
         <v>45927</v>
       </c>
-      <c r="H115" s="46"/>
+      <c r="H115" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="116" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
@@ -3442,7 +3629,7 @@
         <v>37</v>
       </c>
       <c r="E116" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F116" s="48">
         <v>44693</v>
@@ -3450,7 +3637,9 @@
       <c r="G116" s="48">
         <v>45927</v>
       </c>
-      <c r="H116" s="46"/>
+      <c r="H116" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="117" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
@@ -3464,7 +3653,7 @@
         <v>37</v>
       </c>
       <c r="E117" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F117" s="48">
         <v>44693</v>
@@ -3472,7 +3661,9 @@
       <c r="G117" s="48">
         <v>45927</v>
       </c>
-      <c r="H117" s="46"/>
+      <c r="H117" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="118" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
@@ -3486,7 +3677,7 @@
         <v>37</v>
       </c>
       <c r="E118" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F118" s="48">
         <v>44693</v>
@@ -3494,7 +3685,9 @@
       <c r="G118" s="48">
         <v>45927</v>
       </c>
-      <c r="H118" s="46"/>
+      <c r="H118" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="119" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
@@ -3508,7 +3701,7 @@
         <v>37</v>
       </c>
       <c r="E119" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F119" s="48">
         <v>44693</v>
@@ -3516,7 +3709,9 @@
       <c r="G119" s="48">
         <v>45927</v>
       </c>
-      <c r="H119" s="46"/>
+      <c r="H119" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="120" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
@@ -3530,7 +3725,7 @@
         <v>37</v>
       </c>
       <c r="E120" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F120" s="48">
         <v>44693</v>
@@ -3538,7 +3733,9 @@
       <c r="G120" s="48">
         <v>45927</v>
       </c>
-      <c r="H120" s="46"/>
+      <c r="H120" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="121" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
@@ -3552,7 +3749,7 @@
         <v>37</v>
       </c>
       <c r="E121" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F121" s="48">
         <v>44693</v>
@@ -3560,7 +3757,9 @@
       <c r="G121" s="48">
         <v>45927</v>
       </c>
-      <c r="H121" s="46"/>
+      <c r="H121" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="122" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
@@ -3574,7 +3773,7 @@
         <v>37</v>
       </c>
       <c r="E122" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F122" s="48">
         <v>44693</v>
@@ -3582,7 +3781,9 @@
       <c r="G122" s="48">
         <v>45927</v>
       </c>
-      <c r="H122" s="46"/>
+      <c r="H122" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="123" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
@@ -3596,7 +3797,7 @@
         <v>37</v>
       </c>
       <c r="E123" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F123" s="48">
         <v>44693</v>
@@ -3604,7 +3805,9 @@
       <c r="G123" s="48">
         <v>45927</v>
       </c>
-      <c r="H123" s="46"/>
+      <c r="H123" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="124" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
@@ -3618,7 +3821,7 @@
         <v>37</v>
       </c>
       <c r="E124" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F124" s="48">
         <v>44693</v>
@@ -3626,7 +3829,9 @@
       <c r="G124" s="48">
         <v>45927</v>
       </c>
-      <c r="H124" s="46"/>
+      <c r="H124" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="125" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20" t="s">
@@ -3640,7 +3845,7 @@
         <v>37</v>
       </c>
       <c r="E125" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F125" s="48">
         <v>44693</v>
@@ -3648,7 +3853,9 @@
       <c r="G125" s="48">
         <v>45927</v>
       </c>
-      <c r="H125" s="46"/>
+      <c r="H125" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="126" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20" t="s">
@@ -3662,7 +3869,7 @@
         <v>37</v>
       </c>
       <c r="E126" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F126" s="48">
         <v>44693</v>
@@ -3670,7 +3877,9 @@
       <c r="G126" s="48">
         <v>45927</v>
       </c>
-      <c r="H126" s="46"/>
+      <c r="H126" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="127" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
@@ -3684,7 +3893,7 @@
         <v>37</v>
       </c>
       <c r="E127" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F127" s="48">
         <v>44693</v>
@@ -3692,7 +3901,9 @@
       <c r="G127" s="48">
         <v>45927</v>
       </c>
-      <c r="H127" s="46"/>
+      <c r="H127" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="128" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
@@ -3706,7 +3917,7 @@
         <v>37</v>
       </c>
       <c r="E128" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F128" s="48">
         <v>44693</v>
@@ -3714,7 +3925,9 @@
       <c r="G128" s="48">
         <v>45927</v>
       </c>
-      <c r="H128" s="46"/>
+      <c r="H128" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="129" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
@@ -3728,7 +3941,7 @@
         <v>37</v>
       </c>
       <c r="E129" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F129" s="48">
         <v>44693</v>
@@ -3736,7 +3949,9 @@
       <c r="G129" s="48">
         <v>45927</v>
       </c>
-      <c r="H129" s="46"/>
+      <c r="H129" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="130" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
@@ -3750,7 +3965,7 @@
         <v>37</v>
       </c>
       <c r="E130" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F130" s="48">
         <v>44693</v>
@@ -3758,7 +3973,9 @@
       <c r="G130" s="48">
         <v>45927</v>
       </c>
-      <c r="H130" s="46"/>
+      <c r="H130" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="131" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
@@ -3772,7 +3989,7 @@
         <v>43</v>
       </c>
       <c r="E131" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F131" s="48">
         <v>44693</v>
@@ -3780,7 +3997,9 @@
       <c r="G131" s="48">
         <v>45927</v>
       </c>
-      <c r="H131" s="46"/>
+      <c r="H131" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="132" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
@@ -3794,7 +4013,7 @@
         <v>43</v>
       </c>
       <c r="E132" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F132" s="48">
         <v>44693</v>
@@ -3802,7 +4021,9 @@
       <c r="G132" s="48">
         <v>45927</v>
       </c>
-      <c r="H132" s="46"/>
+      <c r="H132" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="133" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
@@ -3816,7 +4037,7 @@
         <v>43</v>
       </c>
       <c r="E133" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F133" s="48">
         <v>44693</v>
@@ -3824,7 +4045,9 @@
       <c r="G133" s="48">
         <v>45927</v>
       </c>
-      <c r="H133" s="46"/>
+      <c r="H133" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="134" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
@@ -3838,7 +4061,7 @@
         <v>43</v>
       </c>
       <c r="E134" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F134" s="48">
         <v>44693</v>
@@ -3846,7 +4069,9 @@
       <c r="G134" s="48">
         <v>45927</v>
       </c>
-      <c r="H134" s="46"/>
+      <c r="H134" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="135" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
@@ -3860,7 +4085,7 @@
         <v>43</v>
       </c>
       <c r="E135" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F135" s="48">
         <v>44693</v>
@@ -3868,7 +4093,9 @@
       <c r="G135" s="48">
         <v>45927</v>
       </c>
-      <c r="H135" s="46"/>
+      <c r="H135" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="136" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
@@ -3882,7 +4109,7 @@
         <v>43</v>
       </c>
       <c r="E136" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F136" s="48">
         <v>44693</v>
@@ -3890,7 +4117,9 @@
       <c r="G136" s="48">
         <v>45927</v>
       </c>
-      <c r="H136" s="46"/>
+      <c r="H136" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="137" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
@@ -3904,7 +4133,7 @@
         <v>43</v>
       </c>
       <c r="E137" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F137" s="48">
         <v>44693</v>
@@ -3912,7 +4141,9 @@
       <c r="G137" s="48">
         <v>45927</v>
       </c>
-      <c r="H137" s="46"/>
+      <c r="H137" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="138" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
@@ -3926,7 +4157,7 @@
         <v>43</v>
       </c>
       <c r="E138" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F138" s="48">
         <v>44693</v>
@@ -3934,7 +4165,9 @@
       <c r="G138" s="48">
         <v>45927</v>
       </c>
-      <c r="H138" s="46"/>
+      <c r="H138" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="139" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
@@ -3948,7 +4181,7 @@
         <v>43</v>
       </c>
       <c r="E139" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F139" s="48">
         <v>44693</v>
@@ -3956,7 +4189,9 @@
       <c r="G139" s="48">
         <v>45927</v>
       </c>
-      <c r="H139" s="46"/>
+      <c r="H139" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="140" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
@@ -3970,7 +4205,7 @@
         <v>43</v>
       </c>
       <c r="E140" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F140" s="48">
         <v>44693</v>
@@ -3978,7 +4213,9 @@
       <c r="G140" s="48">
         <v>45927</v>
       </c>
-      <c r="H140" s="46"/>
+      <c r="H140" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="141" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
@@ -3992,7 +4229,7 @@
         <v>43</v>
       </c>
       <c r="E141" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F141" s="48">
         <v>44693</v>
@@ -4000,7 +4237,9 @@
       <c r="G141" s="48">
         <v>45927</v>
       </c>
-      <c r="H141" s="46"/>
+      <c r="H141" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="142" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
@@ -4014,7 +4253,7 @@
         <v>43</v>
       </c>
       <c r="E142" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F142" s="48">
         <v>44693</v>
@@ -4022,7 +4261,9 @@
       <c r="G142" s="48">
         <v>45927</v>
       </c>
-      <c r="H142" s="46"/>
+      <c r="H142" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="143" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
@@ -4036,7 +4277,7 @@
         <v>43</v>
       </c>
       <c r="E143" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F143" s="48">
         <v>44693</v>
@@ -4044,7 +4285,9 @@
       <c r="G143" s="48">
         <v>45927</v>
       </c>
-      <c r="H143" s="46"/>
+      <c r="H143" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="144" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
@@ -4058,7 +4301,7 @@
         <v>43</v>
       </c>
       <c r="E144" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F144" s="48">
         <v>44693</v>
@@ -4066,7 +4309,9 @@
       <c r="G144" s="48">
         <v>45927</v>
       </c>
-      <c r="H144" s="46"/>
+      <c r="H144" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="145" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
@@ -4080,7 +4325,7 @@
         <v>43</v>
       </c>
       <c r="E145" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F145" s="48">
         <v>44693</v>
@@ -4088,7 +4333,9 @@
       <c r="G145" s="48">
         <v>45927</v>
       </c>
-      <c r="H145" s="46"/>
+      <c r="H145" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="146" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
@@ -4102,7 +4349,7 @@
         <v>43</v>
       </c>
       <c r="E146" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F146" s="48">
         <v>44693</v>
@@ -4110,7 +4357,9 @@
       <c r="G146" s="48">
         <v>45927</v>
       </c>
-      <c r="H146" s="46"/>
+      <c r="H146" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="147" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
@@ -4124,7 +4373,7 @@
         <v>43</v>
       </c>
       <c r="E147" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F147" s="48">
         <v>44693</v>
@@ -4132,7 +4381,9 @@
       <c r="G147" s="48">
         <v>45927</v>
       </c>
-      <c r="H147" s="46"/>
+      <c r="H147" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="148" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
@@ -4146,7 +4397,7 @@
         <v>43</v>
       </c>
       <c r="E148" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F148" s="48">
         <v>44693</v>
@@ -4154,7 +4405,9 @@
       <c r="G148" s="48">
         <v>45927</v>
       </c>
-      <c r="H148" s="46"/>
+      <c r="H148" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="149" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
@@ -4168,7 +4421,7 @@
         <v>43</v>
       </c>
       <c r="E149" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F149" s="48">
         <v>44693</v>
@@ -4176,7 +4429,9 @@
       <c r="G149" s="48">
         <v>45927</v>
       </c>
-      <c r="H149" s="46"/>
+      <c r="H149" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="150" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
@@ -4190,7 +4445,7 @@
         <v>43</v>
       </c>
       <c r="E150" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F150" s="48">
         <v>44693</v>
@@ -4198,7 +4453,9 @@
       <c r="G150" s="48">
         <v>45927</v>
       </c>
-      <c r="H150" s="46"/>
+      <c r="H150" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="151" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
@@ -4212,7 +4469,7 @@
         <v>43</v>
       </c>
       <c r="E151" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F151" s="48">
         <v>44693</v>
@@ -4220,7 +4477,9 @@
       <c r="G151" s="48">
         <v>45927</v>
       </c>
-      <c r="H151" s="46"/>
+      <c r="H151" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="152" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
@@ -4234,7 +4493,7 @@
         <v>43</v>
       </c>
       <c r="E152" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F152" s="48">
         <v>44693</v>
@@ -4242,7 +4501,9 @@
       <c r="G152" s="48">
         <v>45927</v>
       </c>
-      <c r="H152" s="46"/>
+      <c r="H152" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="153" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
@@ -4256,7 +4517,7 @@
         <v>43</v>
       </c>
       <c r="E153" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F153" s="48">
         <v>44693</v>
@@ -4264,7 +4525,9 @@
       <c r="G153" s="48">
         <v>45927</v>
       </c>
-      <c r="H153" s="46"/>
+      <c r="H153" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="154" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
@@ -4278,7 +4541,7 @@
         <v>43</v>
       </c>
       <c r="E154" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F154" s="48">
         <v>44693</v>
@@ -4286,7 +4549,9 @@
       <c r="G154" s="48">
         <v>45927</v>
       </c>
-      <c r="H154" s="46"/>
+      <c r="H154" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="155" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
@@ -4300,7 +4565,7 @@
         <v>43</v>
       </c>
       <c r="E155" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F155" s="48">
         <v>44693</v>
@@ -4308,7 +4573,9 @@
       <c r="G155" s="48">
         <v>45927</v>
       </c>
-      <c r="H155" s="46"/>
+      <c r="H155" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="156" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
@@ -4322,7 +4589,7 @@
         <v>43</v>
       </c>
       <c r="E156" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F156" s="48">
         <v>44693</v>
@@ -4330,7 +4597,9 @@
       <c r="G156" s="48">
         <v>45927</v>
       </c>
-      <c r="H156" s="46"/>
+      <c r="H156" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="157" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
@@ -4344,7 +4613,7 @@
         <v>43</v>
       </c>
       <c r="E157" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F157" s="48">
         <v>44693</v>
@@ -4352,7 +4621,9 @@
       <c r="G157" s="48">
         <v>45927</v>
       </c>
-      <c r="H157" s="46"/>
+      <c r="H157" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="158" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
@@ -4366,7 +4637,7 @@
         <v>43</v>
       </c>
       <c r="E158" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F158" s="48">
         <v>44693</v>
@@ -4374,7 +4645,9 @@
       <c r="G158" s="48">
         <v>45927</v>
       </c>
-      <c r="H158" s="46"/>
+      <c r="H158" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="159" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
@@ -4388,7 +4661,7 @@
         <v>43</v>
       </c>
       <c r="E159" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F159" s="48">
         <v>44693</v>
@@ -4396,7 +4669,9 @@
       <c r="G159" s="48">
         <v>45927</v>
       </c>
-      <c r="H159" s="46"/>
+      <c r="H159" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="160" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
@@ -4410,7 +4685,7 @@
         <v>43</v>
       </c>
       <c r="E160" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F160" s="48">
         <v>44693</v>
@@ -4418,7 +4693,9 @@
       <c r="G160" s="48">
         <v>45927</v>
       </c>
-      <c r="H160" s="46"/>
+      <c r="H160" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="161" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
@@ -4432,7 +4709,7 @@
         <v>43</v>
       </c>
       <c r="E161" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F161" s="48">
         <v>44693</v>
@@ -4440,7 +4717,9 @@
       <c r="G161" s="48">
         <v>45927</v>
       </c>
-      <c r="H161" s="46"/>
+      <c r="H161" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="162" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
@@ -4454,7 +4733,7 @@
         <v>43</v>
       </c>
       <c r="E162" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F162" s="48">
         <v>44693</v>
@@ -4462,7 +4741,9 @@
       <c r="G162" s="48">
         <v>45927</v>
       </c>
-      <c r="H162" s="46"/>
+      <c r="H162" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="163" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
@@ -4476,7 +4757,7 @@
         <v>43</v>
       </c>
       <c r="E163" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F163" s="48">
         <v>44693</v>
@@ -4484,7 +4765,9 @@
       <c r="G163" s="48">
         <v>45927</v>
       </c>
-      <c r="H163" s="46"/>
+      <c r="H163" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="164" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
@@ -4498,7 +4781,7 @@
         <v>43</v>
       </c>
       <c r="E164" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F164" s="48">
         <v>44693</v>
@@ -4506,7 +4789,9 @@
       <c r="G164" s="48">
         <v>45927</v>
       </c>
-      <c r="H164" s="46"/>
+      <c r="H164" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="165" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
@@ -4520,7 +4805,7 @@
         <v>43</v>
       </c>
       <c r="E165" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F165" s="48">
         <v>44693</v>
@@ -4528,7 +4813,9 @@
       <c r="G165" s="48">
         <v>45927</v>
       </c>
-      <c r="H165" s="46"/>
+      <c r="H165" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="166" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
@@ -4542,7 +4829,7 @@
         <v>43</v>
       </c>
       <c r="E166" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F166" s="48">
         <v>44693</v>
@@ -4550,7 +4837,9 @@
       <c r="G166" s="48">
         <v>45927</v>
       </c>
-      <c r="H166" s="46"/>
+      <c r="H166" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="167" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
@@ -4564,7 +4853,7 @@
         <v>43</v>
       </c>
       <c r="E167" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F167" s="48">
         <v>44693</v>
@@ -4572,7 +4861,9 @@
       <c r="G167" s="48">
         <v>45927</v>
       </c>
-      <c r="H167" s="46"/>
+      <c r="H167" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="168" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
@@ -4586,7 +4877,7 @@
         <v>43</v>
       </c>
       <c r="E168" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F168" s="48">
         <v>44693</v>
@@ -4594,7 +4885,9 @@
       <c r="G168" s="48">
         <v>45927</v>
       </c>
-      <c r="H168" s="46"/>
+      <c r="H168" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="169" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
@@ -4608,7 +4901,7 @@
         <v>43</v>
       </c>
       <c r="E169" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F169" s="48">
         <v>44693</v>
@@ -4616,7 +4909,9 @@
       <c r="G169" s="48">
         <v>45927</v>
       </c>
-      <c r="H169" s="46"/>
+      <c r="H169" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="170" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
@@ -4630,7 +4925,7 @@
         <v>43</v>
       </c>
       <c r="E170" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F170" s="48">
         <v>44693</v>
@@ -4638,7 +4933,9 @@
       <c r="G170" s="48">
         <v>45927</v>
       </c>
-      <c r="H170" s="46"/>
+      <c r="H170" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="171" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
@@ -4652,7 +4949,7 @@
         <v>43</v>
       </c>
       <c r="E171" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F171" s="48">
         <v>44693</v>
@@ -4660,7 +4957,9 @@
       <c r="G171" s="48">
         <v>45927</v>
       </c>
-      <c r="H171" s="46"/>
+      <c r="H171" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="172" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
@@ -4674,7 +4973,7 @@
         <v>43</v>
       </c>
       <c r="E172" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F172" s="48">
         <v>44693</v>
@@ -4682,7 +4981,9 @@
       <c r="G172" s="48">
         <v>45927</v>
       </c>
-      <c r="H172" s="46"/>
+      <c r="H172" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="173" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
@@ -4696,7 +4997,7 @@
         <v>43</v>
       </c>
       <c r="E173" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F173" s="48">
         <v>44693</v>
@@ -4704,7 +5005,9 @@
       <c r="G173" s="48">
         <v>45927</v>
       </c>
-      <c r="H173" s="46"/>
+      <c r="H173" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="174" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
@@ -4718,7 +5021,7 @@
         <v>43</v>
       </c>
       <c r="E174" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F174" s="48">
         <v>44693</v>
@@ -4726,7 +5029,9 @@
       <c r="G174" s="48">
         <v>45927</v>
       </c>
-      <c r="H174" s="46"/>
+      <c r="H174" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="175" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
@@ -4740,7 +5045,7 @@
         <v>43</v>
       </c>
       <c r="E175" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F175" s="48">
         <v>44693</v>
@@ -4748,7 +5053,9 @@
       <c r="G175" s="48">
         <v>45927</v>
       </c>
-      <c r="H175" s="46"/>
+      <c r="H175" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="176" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
@@ -4762,7 +5069,7 @@
         <v>43</v>
       </c>
       <c r="E176" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F176" s="48">
         <v>44693</v>
@@ -4770,7 +5077,9 @@
       <c r="G176" s="48">
         <v>45927</v>
       </c>
-      <c r="H176" s="46"/>
+      <c r="H176" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="177" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
@@ -4784,7 +5093,7 @@
         <v>43</v>
       </c>
       <c r="E177" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F177" s="48">
         <v>44693</v>
@@ -4792,7 +5101,9 @@
       <c r="G177" s="48">
         <v>45927</v>
       </c>
-      <c r="H177" s="46"/>
+      <c r="H177" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="178" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
@@ -4806,7 +5117,7 @@
         <v>43</v>
       </c>
       <c r="E178" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F178" s="48">
         <v>44693</v>
@@ -4814,7 +5125,9 @@
       <c r="G178" s="48">
         <v>45927</v>
       </c>
-      <c r="H178" s="46"/>
+      <c r="H178" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="179" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="19" t="s">
@@ -4828,7 +5141,7 @@
         <v>43</v>
       </c>
       <c r="E179" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F179" s="48">
         <v>44693</v>
@@ -4836,7 +5149,9 @@
       <c r="G179" s="48">
         <v>45927</v>
       </c>
-      <c r="H179" s="46"/>
+      <c r="H179" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="180" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
@@ -4850,7 +5165,7 @@
         <v>43</v>
       </c>
       <c r="E180" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F180" s="48">
         <v>44693</v>
@@ -4858,7 +5173,9 @@
       <c r="G180" s="48">
         <v>45927</v>
       </c>
-      <c r="H180" s="46"/>
+      <c r="H180" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="181" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
@@ -4872,7 +5189,7 @@
         <v>43</v>
       </c>
       <c r="E181" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F181" s="48">
         <v>44693</v>
@@ -4880,7 +5197,9 @@
       <c r="G181" s="48">
         <v>45927</v>
       </c>
-      <c r="H181" s="46"/>
+      <c r="H181" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="182" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
@@ -4894,7 +5213,7 @@
         <v>43</v>
       </c>
       <c r="E182" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F182" s="48">
         <v>44693</v>
@@ -4902,7 +5221,9 @@
       <c r="G182" s="48">
         <v>45927</v>
       </c>
-      <c r="H182" s="46"/>
+      <c r="H182" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="183" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
@@ -4916,7 +5237,7 @@
         <v>43</v>
       </c>
       <c r="E183" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F183" s="48">
         <v>44693</v>
@@ -4924,7 +5245,9 @@
       <c r="G183" s="48">
         <v>45927</v>
       </c>
-      <c r="H183" s="46"/>
+      <c r="H183" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="184" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
@@ -4938,7 +5261,7 @@
         <v>43</v>
       </c>
       <c r="E184" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F184" s="48">
         <v>44693</v>
@@ -4946,7 +5269,9 @@
       <c r="G184" s="48">
         <v>45927</v>
       </c>
-      <c r="H184" s="46"/>
+      <c r="H184" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="185" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
@@ -4960,7 +5285,7 @@
         <v>43</v>
       </c>
       <c r="E185" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F185" s="48">
         <v>44693</v>
@@ -4968,7 +5293,9 @@
       <c r="G185" s="48">
         <v>45927</v>
       </c>
-      <c r="H185" s="46"/>
+      <c r="H185" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="186" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
@@ -4982,7 +5309,7 @@
         <v>43</v>
       </c>
       <c r="E186" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F186" s="48">
         <v>44693</v>
@@ -4990,7 +5317,9 @@
       <c r="G186" s="48">
         <v>45927</v>
       </c>
-      <c r="H186" s="46"/>
+      <c r="H186" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="187" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
@@ -5004,7 +5333,7 @@
         <v>43</v>
       </c>
       <c r="E187" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F187" s="48">
         <v>44693</v>
@@ -5012,7 +5341,9 @@
       <c r="G187" s="48">
         <v>45927</v>
       </c>
-      <c r="H187" s="46"/>
+      <c r="H187" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="188" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
@@ -5026,7 +5357,7 @@
         <v>43</v>
       </c>
       <c r="E188" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F188" s="48">
         <v>44693</v>
@@ -5034,7 +5365,9 @@
       <c r="G188" s="48">
         <v>45927</v>
       </c>
-      <c r="H188" s="46"/>
+      <c r="H188" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="189" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
@@ -5048,7 +5381,7 @@
         <v>43</v>
       </c>
       <c r="E189" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F189" s="48">
         <v>44693</v>
@@ -5056,7 +5389,9 @@
       <c r="G189" s="48">
         <v>45927</v>
       </c>
-      <c r="H189" s="46"/>
+      <c r="H189" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="190" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
@@ -5070,7 +5405,7 @@
         <v>43</v>
       </c>
       <c r="E190" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F190" s="48">
         <v>44693</v>
@@ -5078,7 +5413,9 @@
       <c r="G190" s="48">
         <v>45927</v>
       </c>
-      <c r="H190" s="46"/>
+      <c r="H190" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="191" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
@@ -5092,7 +5429,7 @@
         <v>43</v>
       </c>
       <c r="E191" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F191" s="48">
         <v>44693</v>
@@ -5100,7 +5437,9 @@
       <c r="G191" s="48">
         <v>45927</v>
       </c>
-      <c r="H191" s="46"/>
+      <c r="H191" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="192" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
@@ -5114,7 +5453,7 @@
         <v>43</v>
       </c>
       <c r="E192" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F192" s="48">
         <v>44693</v>
@@ -5122,7 +5461,9 @@
       <c r="G192" s="48">
         <v>45927</v>
       </c>
-      <c r="H192" s="46"/>
+      <c r="H192" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="193" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
@@ -5136,7 +5477,7 @@
         <v>43</v>
       </c>
       <c r="E193" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F193" s="48">
         <v>44693</v>
@@ -5144,7 +5485,9 @@
       <c r="G193" s="48">
         <v>45927</v>
       </c>
-      <c r="H193" s="46"/>
+      <c r="H193" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="194" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
@@ -5158,7 +5501,7 @@
         <v>43</v>
       </c>
       <c r="E194" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F194" s="48">
         <v>44693</v>
@@ -5166,7 +5509,9 @@
       <c r="G194" s="48">
         <v>45927</v>
       </c>
-      <c r="H194" s="46"/>
+      <c r="H194" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="195" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
@@ -5180,7 +5525,7 @@
         <v>43</v>
       </c>
       <c r="E195" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F195" s="48">
         <v>44693</v>
@@ -5188,7 +5533,9 @@
       <c r="G195" s="48">
         <v>45927</v>
       </c>
-      <c r="H195" s="46"/>
+      <c r="H195" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="196" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
@@ -5202,7 +5549,7 @@
         <v>43</v>
       </c>
       <c r="E196" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F196" s="48">
         <v>44693</v>
@@ -5210,7 +5557,9 @@
       <c r="G196" s="48">
         <v>45927</v>
       </c>
-      <c r="H196" s="46"/>
+      <c r="H196" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="197" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
@@ -5224,7 +5573,7 @@
         <v>43</v>
       </c>
       <c r="E197" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F197" s="48">
         <v>44693</v>
@@ -5232,7 +5581,9 @@
       <c r="G197" s="48">
         <v>45927</v>
       </c>
-      <c r="H197" s="46"/>
+      <c r="H197" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="198" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
@@ -5246,7 +5597,7 @@
         <v>43</v>
       </c>
       <c r="E198" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F198" s="48">
         <v>44693</v>
@@ -5254,7 +5605,9 @@
       <c r="G198" s="48">
         <v>45927</v>
       </c>
-      <c r="H198" s="46"/>
+      <c r="H198" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="199" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
@@ -5268,7 +5621,7 @@
         <v>43</v>
       </c>
       <c r="E199" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F199" s="48">
         <v>44693</v>
@@ -5276,7 +5629,9 @@
       <c r="G199" s="48">
         <v>45927</v>
       </c>
-      <c r="H199" s="46"/>
+      <c r="H199" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="200" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
@@ -5290,7 +5645,7 @@
         <v>43</v>
       </c>
       <c r="E200" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F200" s="48">
         <v>44693</v>
@@ -5298,7 +5653,9 @@
       <c r="G200" s="48">
         <v>45927</v>
       </c>
-      <c r="H200" s="46"/>
+      <c r="H200" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="201" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="13" t="s">
@@ -5312,7 +5669,7 @@
         <v>43</v>
       </c>
       <c r="E201" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F201" s="48">
         <v>44693</v>
@@ -5320,7 +5677,9 @@
       <c r="G201" s="48">
         <v>45927</v>
       </c>
-      <c r="H201" s="46"/>
+      <c r="H201" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="202" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
@@ -5334,7 +5693,7 @@
         <v>43</v>
       </c>
       <c r="E202" s="46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F202" s="48">
         <v>44693</v>
@@ -5342,7 +5701,9 @@
       <c r="G202" s="48">
         <v>45927</v>
       </c>
-      <c r="H202" s="46"/>
+      <c r="H202" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="203" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="12"/>
